--- a/outputs/evaluation/architecture/design/v1/CF_M01/run_1/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v1/CF_M01/run_1/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.5</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.5625</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9869</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.869</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.8179</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_06', 'AU_07', 'AU_08']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_19</t>
@@ -1233,7 +1245,6 @@
           <t>api gateway, core, mòdul analític</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU26</t>
@@ -1308,13 +1318,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -1338,13 +1346,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1390,13 +1396,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1447,7 +1449,6 @@
       <c r="D5" t="n">
         <v>0.9201</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1468,7 +1469,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_18</t>
@@ -1479,7 +1479,6 @@
           <t>presentation layer, api gateway</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1498,7 +1497,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -1554,13 +1552,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1718,13 +1708,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -1748,13 +1736,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1800,13 +1786,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -1830,13 +1814,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1877,14 +1859,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -1908,13 +1887,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1960,13 +1937,11 @@
           <t>['AU_06', 'AU_07', 'AU_08', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -1990,13 +1965,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2037,14 +2010,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2120,13 +2088,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -2150,13 +2116,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2202,13 +2166,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2232,13 +2194,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2284,13 +2244,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -2314,13 +2272,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2361,14 +2317,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -2392,13 +2345,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2444,13 +2395,11 @@
           <t>['P_01']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Three Layers</t>
@@ -2474,13 +2423,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2526,13 +2473,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -2558,13 +2503,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2605,14 +2548,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -2631,14 +2571,11 @@
       <c r="P19" t="n">
         <v>41</v>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2679,14 +2616,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -2710,13 +2644,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2762,13 +2694,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -2792,13 +2722,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2872,7 +2800,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -2908,7 +2835,6 @@
           <t>Mòdul analític</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>This service has the main function of obtaining and processing playlog, connection, and platform action data.</t>
@@ -3000,7 +2926,6 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>A player consists of a device that can be internal or external, which allows screens to reproduce content on the screens.</t>
@@ -3036,7 +2961,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -3067,7 +2991,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -3083,7 +3006,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>0.8168</v>
       </c>
@@ -3104,7 +3026,6 @@
           <t>HTTP</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -3115,7 +3036,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.8018999999999999</v>
       </c>
@@ -3136,7 +3056,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -3172,7 +3091,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -3183,7 +3101,6 @@
           <t>AU_18</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>0.7501</v>
       </c>
@@ -3204,7 +3121,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -3235,7 +3151,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -3276,7 +3191,6 @@
           <t>TCP</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>communication between the Api Gateway service is via the TCP communication protocol</t>
@@ -3287,7 +3201,6 @@
           <t>AU_19</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>0.7254</v>
       </c>
@@ -3308,7 +3221,6 @@
           <t>Analytical module</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Its main function is to obtain and process data from playlogs, connections and platform actions. This service mainly interacts with cloud services, although it also interacts to a lesser extent with the database.</t>
@@ -3339,7 +3251,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>player, api player</t>
@@ -3375,7 +3286,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>player, web socket</t>
@@ -3416,7 +3326,6 @@
           <t>SQL database</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. [...] The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system. This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -3452,7 +3361,6 @@
           <t>AWS cloud services set</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>As can be seen in Figure 9.1, the data layer is made up of AWS cloud services and the database. […] The objective of these services is to form a data lake where all the historical data is stored in order to process them in the analytical module.</t>
@@ -3488,7 +3396,6 @@
           <t>MySQL</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
@@ -3524,7 +3431,6 @@
           <t>TypeScript</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>This programming language is built on top of JavaScript, it extends the JavaScript syntax.</t>
@@ -3560,7 +3466,6 @@
           <t>AWS RDS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -3591,7 +3496,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>analytical module, aws cloud services set, sql database</t>
@@ -3627,7 +3531,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>core service, sql database, aws cloud services set</t>
@@ -3668,7 +3571,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
